--- a/Administración de Sistemas/Unidad 3 - Procesos/Procesos.xlsx
+++ b/Administración de Sistemas/Unidad 3 - Procesos/Procesos.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA58D974-1A8B-473E-BA4B-8FCE1430976F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Folla1" sheetId="1" r:id="rId1"/>
     <sheet name="Folla2" sheetId="2" r:id="rId2"/>
     <sheet name="Folla3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
   <si>
     <t>P1</t>
   </si>
@@ -283,15 +277,15 @@
     <t>TEMPO DE ESPERA - CICLOS CPU</t>
   </si>
   <si>
-    <t>Con q = 2 ut</t>
+    <t>Con q = 1 ut</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -483,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -498,7 +492,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -512,25 +506,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -542,9 +524,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -578,6 +557,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,9 +578,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -636,7 +618,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -708,7 +690,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -881,41 +863,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X55"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
     </row>
     <row r="2" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
@@ -929,7 +911,7 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="19">
@@ -940,13 +922,13 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <v>10</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -954,16 +936,16 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="21">
         <v>2</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="21">
         <v>3</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>28</v>
       </c>
       <c r="H5" t="s">
@@ -971,33 +953,33 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="22">
         <v>2</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="22">
         <v>4</v>
       </c>
-      <c r="E6" s="29"/>
+      <c r="E6" s="25"/>
       <c r="K6" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <v>6</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="28" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1083,7 +1065,7 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="3">
@@ -1126,7 +1108,7 @@
         <f>B4/N11*100</f>
         <v>90.909090909090907</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -1159,17 +1141,17 @@
         <f>B5/P11*100</f>
         <v>15.384615384615385</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="3"/>
@@ -1192,19 +1174,19 @@
         <f>B6/R11*100</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="3"/>
@@ -1225,21 +1207,21 @@
         <f>B7/X11*100</f>
         <v>28.571428571428569</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
@@ -1325,7 +1307,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="3">
@@ -1400,12 +1382,12 @@
         <v>22.222222222222221</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="3"/>
@@ -1565,7 +1547,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="3">
@@ -1613,13 +1595,13 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="35"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="30"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
@@ -1641,7 +1623,7 @@
         <f>B5/B31*100</f>
         <v>66.666666666666657</v>
       </c>
-      <c r="D31" s="34"/>
+      <c r="D31" s="29"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="3"/>
@@ -1675,8 +1657,8 @@
         <v>40</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="3"/>
@@ -1710,8 +1692,8 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -1733,7 +1715,7 @@
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="30" t="s">
+      <c r="F36" s="26" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1810,7 +1792,7 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="3">
@@ -1820,7 +1802,7 @@
         <f>B3/D20*100</f>
         <v>100</v>
       </c>
-      <c r="D38" s="28"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1843,7 +1825,7 @@
       <c r="X38" s="3"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B39" s="3">
@@ -1854,35 +1836,41 @@
         <v>4.7619047619047619</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35">
+      <c r="E39" s="5">
+        <v>9</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="5">
         <v>8</v>
       </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35">
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="5">
+        <v>7</v>
+      </c>
+      <c r="N39" s="29"/>
+      <c r="O39" s="5">
         <v>6</v>
       </c>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35">
+      <c r="P39" s="29"/>
+      <c r="Q39" s="5">
+        <v>5</v>
+      </c>
+      <c r="R39" s="29"/>
+      <c r="S39" s="5">
         <v>4</v>
       </c>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="3">
@@ -1893,29 +1881,31 @@
         <v>220.00000000000003</v>
       </c>
       <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="6">
+        <v>1</v>
+      </c>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="39" t="s">
+      <c r="A41" s="34" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="3">
@@ -1926,29 +1916,31 @@
         <v>185.71428571428572</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="29"/>
+      <c r="X41" s="29"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="37" t="s">
+      <c r="A42" s="32" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="3">
@@ -1959,30 +1951,36 @@
         <v>88.235294117647058</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="8"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="8">
+        <v>5</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
       <c r="L42" s="8">
         <v>4</v>
       </c>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="8"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="8">
+        <v>3</v>
+      </c>
+      <c r="O42" s="29"/>
       <c r="P42" s="8">
         <v>2</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="8"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="8">
+        <v>1</v>
+      </c>
+      <c r="S42" s="29"/>
       <c r="T42" s="8"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="29"/>
+      <c r="X42" s="29"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1994,100 +1992,34 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="19">
-        <v>1</v>
-      </c>
-      <c r="C59" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="21">
-        <v>10</v>
-      </c>
-      <c r="C60" s="21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B61" s="23">
-        <v>2</v>
-      </c>
-      <c r="C61" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="25">
-        <v>2</v>
-      </c>
-      <c r="C62" s="25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="27">
-        <v>6</v>
-      </c>
-      <c r="C63" s="27">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2100,18 +2032,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Administración de Sistemas/Unidad 3 - Procesos/Procesos.xlsx
+++ b/Administración de Sistemas/Unidad 3 - Procesos/Procesos.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>P1</t>
   </si>
@@ -272,9 +272,6 @@
   </si>
   <si>
     <t>Espera</t>
-  </si>
-  <si>
-    <t>TEMPO DE ESPERA - CICLOS CPU</t>
   </si>
   <si>
     <t>Con q = 1 ut</t>
@@ -477,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -495,8 +492,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -560,6 +555,10 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,63 +871,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
     </row>
     <row r="2" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="17">
         <v>1</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>10</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -936,50 +935,50 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>2</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <v>3</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>28</v>
+      <c r="E5" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="20">
         <v>2</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="20">
         <v>4</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="23"/>
       <c r="K6" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="21">
         <v>6</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="21">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="26" t="s">
         <v>26</v>
       </c>
     </row>
@@ -988,19 +987,17 @@
         <v>5</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="K10" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="42">
         <v>1</v>
       </c>
       <c r="E11" s="3">
@@ -1030,19 +1027,19 @@
       <c r="M11" s="3">
         <v>10</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="42">
         <v>11</v>
       </c>
       <c r="O11" s="3">
         <v>12</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="42">
         <v>13</v>
       </c>
       <c r="Q11" s="3">
         <v>14</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="42">
         <v>15</v>
       </c>
       <c r="S11" s="3">
@@ -1060,12 +1057,12 @@
       <c r="W11" s="3">
         <v>20</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="42">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="3">
@@ -1108,7 +1105,7 @@
         <f>B4/N11*100</f>
         <v>90.909090909090907</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -1141,17 +1138,17 @@
         <f>B5/P11*100</f>
         <v>15.384615384615385</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="3"/>
@@ -1174,19 +1171,19 @@
         <f>B6/R11*100</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="3"/>
@@ -1207,21 +1204,21 @@
         <f>B7/X11*100</f>
         <v>28.571428571428569</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
@@ -1229,6 +1226,12 @@
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
     </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C17" s="40">
+        <f>SUM(C12:C16)/5</f>
+        <v>49.639693639693647</v>
+      </c>
+    </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
@@ -1236,13 +1239,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="43">
         <v>1</v>
       </c>
       <c r="E20" s="3">
@@ -1260,19 +1263,19 @@
       <c r="I20" s="3">
         <v>6</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="42">
         <v>7</v>
       </c>
       <c r="K20" s="3">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="42">
         <v>9</v>
       </c>
       <c r="M20" s="3">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="42">
         <v>11</v>
       </c>
       <c r="O20" s="3">
@@ -1302,12 +1305,12 @@
       <c r="W20" s="3">
         <v>20</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="42">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="3">
@@ -1344,21 +1347,23 @@
         <v>1</v>
       </c>
       <c r="B22" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C22" s="13">
-        <f>B4/B22*100</f>
+        <f>B4/X20*100</f>
         <v>47.619047619047613</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
@@ -1375,19 +1380,19 @@
         <v>2</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" s="13">
-        <f>B5/B23*100</f>
+        <f>B5/L20*100</f>
         <v>22.222222222222221</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="3"/>
@@ -1408,21 +1413,21 @@
         <v>3</v>
       </c>
       <c r="B24" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C24" s="13">
-        <f>B6/B24*100</f>
+        <f>B6/N20*100</f>
         <v>18.181818181818183</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="3"/>
@@ -1441,13 +1446,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C25" s="13">
-        <f>B7/B25*100</f>
+        <f>B7/J20*100</f>
         <v>85.714285714285708</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -1469,6 +1474,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C26" s="40">
+        <f>SUM(C21:C25)/5</f>
+        <v>54.747474747474747</v>
+      </c>
+    </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>8</v>
@@ -1476,25 +1487,25 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="42">
         <v>1</v>
       </c>
       <c r="E28" s="3">
         <v>2</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="42">
         <v>3</v>
       </c>
       <c r="G28" s="3">
         <v>4</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="42">
         <v>5</v>
       </c>
       <c r="I28" s="3">
@@ -1512,7 +1523,7 @@
       <c r="M28" s="3">
         <v>10</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="42">
         <v>11</v>
       </c>
       <c r="O28" s="3">
@@ -1542,19 +1553,19 @@
       <c r="W28" s="3">
         <v>20</v>
       </c>
-      <c r="X28" s="3">
+      <c r="X28" s="42">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="3">
         <v>0</v>
       </c>
       <c r="C29" s="13">
-        <f>B3/D20*100</f>
+        <f>B3/D37*100</f>
         <v>100</v>
       </c>
       <c r="D29" s="4"/>
@@ -1584,24 +1595,24 @@
         <v>1</v>
       </c>
       <c r="B30" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C30" s="13">
-        <f>B4/B30*100</f>
+        <f>B4/X28*100</f>
         <v>47.619047619047613</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="30"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="28"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
@@ -1617,13 +1628,13 @@
         <v>2</v>
       </c>
       <c r="B31" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="13">
-        <f>B5/B31*100</f>
+        <f>B5/3*100</f>
         <v>66.666666666666657</v>
       </c>
-      <c r="D31" s="29"/>
+      <c r="D31" s="25"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="3"/>
@@ -1650,15 +1661,15 @@
         <v>3</v>
       </c>
       <c r="B32" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C32" s="13">
-        <f>B6/B32*100</f>
+        <f>B6/H28*100</f>
         <v>40</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="3"/>
@@ -1683,17 +1694,17 @@
         <v>4</v>
       </c>
       <c r="B33" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C33" s="13">
-        <f>B7/B33*100</f>
+        <f>B7/N28*100</f>
         <v>54.54545454545454</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -1711,23 +1722,29 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
     </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C34" s="40">
+        <f>SUM(C29:C33)/5</f>
+        <v>61.766233766233768</v>
+      </c>
+    </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="26" t="s">
-        <v>28</v>
+      <c r="F36" s="24" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="42">
         <v>1</v>
       </c>
       <c r="E37" s="3">
@@ -1745,10 +1762,10 @@
       <c r="I37" s="3">
         <v>6</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="42">
         <v>7</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="42">
         <v>8</v>
       </c>
       <c r="L37" s="3">
@@ -1775,7 +1792,7 @@
       <c r="S37" s="3">
         <v>16</v>
       </c>
-      <c r="T37" s="3">
+      <c r="T37" s="42">
         <v>17</v>
       </c>
       <c r="U37" s="3">
@@ -1787,22 +1804,22 @@
       <c r="W37" s="3">
         <v>20</v>
       </c>
-      <c r="X37" s="3">
+      <c r="X37" s="42">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
       </c>
       <c r="C38" s="13">
-        <f>B3/D20*100</f>
+        <f>B3/D37*100</f>
         <v>100</v>
       </c>
-      <c r="D38" s="24"/>
+      <c r="D38" s="22"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1825,162 +1842,168 @@
       <c r="X38" s="3"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B39" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C39" s="13">
-        <f>B13/B39*100</f>
-        <v>4.7619047619047619</v>
-      </c>
-      <c r="D39" s="3"/>
+        <f>B4/X37*100</f>
+        <v>47.619047619047613</v>
+      </c>
+      <c r="D39" s="25"/>
       <c r="E39" s="5">
         <v>9</v>
       </c>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
       <c r="I39" s="5">
         <v>8</v>
       </c>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
       <c r="M39" s="5">
         <v>7</v>
       </c>
-      <c r="N39" s="29"/>
+      <c r="N39" s="25"/>
       <c r="O39" s="5">
         <v>6</v>
       </c>
-      <c r="P39" s="29"/>
+      <c r="P39" s="25"/>
       <c r="Q39" s="5">
         <v>5</v>
       </c>
-      <c r="R39" s="29"/>
+      <c r="R39" s="25"/>
       <c r="S39" s="5">
         <v>4</v>
       </c>
-      <c r="T39" s="29"/>
+      <c r="T39" s="25"/>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="33" t="s">
+      <c r="A40" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="3">
         <v>5</v>
       </c>
       <c r="C40" s="13">
-        <f>B14/B40*100</f>
-        <v>220.00000000000003</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="29"/>
+        <f>B5/J37*100</f>
+        <v>28.571428571428569</v>
+      </c>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
       <c r="F40" s="6">
         <v>1</v>
       </c>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="32" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="13">
-        <f>B15/B41*100</f>
-        <v>185.71428571428572</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
+        <f>B6/K37*100</f>
+        <v>25</v>
+      </c>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
       <c r="G41" s="7">
         <v>1</v>
       </c>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-      <c r="W41" s="29"/>
-      <c r="X41" s="29"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+      <c r="W41" s="27"/>
+      <c r="X41" s="27"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="30" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C42" s="13">
-        <f>B16/B42*100</f>
-        <v>88.235294117647058</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
+        <f>B7/T37</f>
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
       <c r="H42" s="8">
         <v>5</v>
       </c>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
       <c r="L42" s="8">
         <v>4</v>
       </c>
-      <c r="M42" s="29"/>
+      <c r="M42" s="25"/>
       <c r="N42" s="8">
         <v>3</v>
       </c>
-      <c r="O42" s="29"/>
+      <c r="O42" s="25"/>
       <c r="P42" s="8">
         <v>2</v>
       </c>
-      <c r="Q42" s="29"/>
+      <c r="Q42" s="25"/>
       <c r="R42" s="8">
         <v>1</v>
       </c>
-      <c r="S42" s="29"/>
+      <c r="S42" s="25"/>
       <c r="T42" s="8"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="29"/>
-      <c r="X42" s="29"/>
+      <c r="U42" s="27"/>
+      <c r="V42" s="27"/>
+      <c r="W42" s="27"/>
+      <c r="X42" s="27"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C43" s="40">
+        <f>SUM(C38:C42)/5</f>
+        <v>40.308683473389358</v>
+      </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
